--- a/artfynd/A 9566-2025 artfynd.xlsx
+++ b/artfynd/A 9566-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125297670</v>
+        <v>125296849</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589347</v>
+        <v>589642</v>
       </c>
       <c r="R2" t="n">
-        <v>6932010</v>
+        <v>6932043</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:49</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125298114</v>
+        <v>125299074</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,31 +799,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -842,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589559</v>
+        <v>589570</v>
       </c>
       <c r="R3" t="n">
-        <v>6931779</v>
+        <v>6931668</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Misstänkt natt träd</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125299639</v>
+        <v>125296571</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,48 +925,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589495</v>
+        <v>589603</v>
       </c>
       <c r="R4" t="n">
-        <v>6931745</v>
+        <v>6931964</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1018,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,19 +1009,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125301710</v>
+        <v>125296301</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1081,7 +1057,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1090,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589415</v>
+        <v>589577</v>
       </c>
       <c r="R5" t="n">
-        <v>6931910</v>
+        <v>6932028</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1125,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1135,12 +1111,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Trummande tretå.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1167,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125296182</v>
+        <v>125297742</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1183,16 +1159,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1212,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589542</v>
+        <v>589316</v>
       </c>
       <c r="R6" t="n">
-        <v>6932034</v>
+        <v>6931994</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1247,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1257,7 +1233,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125299018</v>
+        <v>125297670</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1300,39 +1281,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589580</v>
+        <v>589347</v>
       </c>
       <c r="R7" t="n">
-        <v>6931659</v>
+        <v>6932010</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1364,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1374,7 +1355,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,22 +1375,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125296849</v>
+        <v>125296740</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1417,24 +1403,29 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kångeråbäcken, Mpd</t>
@@ -1476,7 +1467,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,7 +1477,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1513,10 +1509,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125299074</v>
+        <v>125301710</v>
       </c>
       <c r="B9" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1525,43 +1521,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589570</v>
+        <v>589415</v>
       </c>
       <c r="R9" t="n">
-        <v>6931668</v>
+        <v>6931910</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1593,7 +1589,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1603,12 +1599,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Misstänkt natt träd</t>
+          <t>Trummande tretå.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1623,19 +1619,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125296711</v>
+        <v>125297600</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1671,14 +1667,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589389</v>
+        <v>589363</v>
       </c>
       <c r="R10" t="n">
-        <v>6931877</v>
+        <v>6932050</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1710,7 +1706,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1720,7 +1716,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1735,22 +1731,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125297544</v>
+        <v>125299018</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1763,27 +1759,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1792,10 +1788,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589525</v>
+        <v>589580</v>
       </c>
       <c r="R11" t="n">
-        <v>6931804</v>
+        <v>6931659</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1827,7 +1823,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1837,12 +1833,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:43</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1869,10 +1860,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125297600</v>
+        <v>125296182</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1885,34 +1876,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589363</v>
+        <v>589542</v>
       </c>
       <c r="R12" t="n">
-        <v>6932050</v>
+        <v>6932034</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1944,7 +1940,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1954,7 +1950,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1981,10 +1977,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125299459</v>
+        <v>125295640</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1997,39 +1993,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589543</v>
+        <v>589461</v>
       </c>
       <c r="R13" t="n">
-        <v>6931727</v>
+        <v>6932074</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2061,7 +2057,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2071,12 +2067,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:51</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på tall</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2091,22 +2082,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125295606</v>
+        <v>125296618</v>
       </c>
       <c r="B14" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2115,31 +2106,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2148,10 +2139,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589420</v>
+        <v>589671</v>
       </c>
       <c r="R14" t="n">
-        <v>6932027</v>
+        <v>6931998</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2183,7 +2174,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2193,7 +2184,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2220,10 +2211,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125296789</v>
+        <v>125295606</v>
       </c>
       <c r="B15" t="n">
-        <v>96979</v>
+        <v>56722</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2236,34 +2227,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589642</v>
+        <v>589420</v>
       </c>
       <c r="R15" t="n">
-        <v>6932043</v>
+        <v>6932027</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2295,7 +2291,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2305,7 +2301,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2332,10 +2328,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125296571</v>
+        <v>125299639</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2348,34 +2344,48 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589603</v>
+        <v>589495</v>
       </c>
       <c r="R16" t="n">
-        <v>6931964</v>
+        <v>6931745</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2407,7 +2417,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2417,7 +2427,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2432,22 +2442,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125296618</v>
+        <v>125297656</v>
       </c>
       <c r="B17" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2460,16 +2470,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2480,19 +2490,19 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589671</v>
+        <v>589540</v>
       </c>
       <c r="R17" t="n">
-        <v>6931998</v>
+        <v>6931801</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2524,7 +2534,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2534,7 +2544,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2549,22 +2564,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125296301</v>
+        <v>125296789</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>96979</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2573,43 +2588,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589577</v>
+        <v>589642</v>
       </c>
       <c r="R18" t="n">
-        <v>6932028</v>
+        <v>6932043</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2641,7 +2651,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2651,12 +2661,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:49</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2683,7 +2688,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125295328</v>
+        <v>125297544</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2719,19 +2724,19 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589415</v>
+        <v>589525</v>
       </c>
       <c r="R19" t="n">
-        <v>6932018</v>
+        <v>6931804</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2763,7 +2768,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2773,12 +2778,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2793,19 +2798,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125296955</v>
+        <v>125298114</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2846,14 +2851,14 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589631</v>
+        <v>589559</v>
       </c>
       <c r="R20" t="n">
-        <v>6932054</v>
+        <v>6931779</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2885,7 +2890,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2895,12 +2900,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2915,19 +2920,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125297656</v>
+        <v>125297753</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2963,7 +2968,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2972,10 +2977,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589540</v>
+        <v>589545</v>
       </c>
       <c r="R21" t="n">
-        <v>6931801</v>
+        <v>6931796</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3007,7 +3012,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3017,7 +3022,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3049,7 +3054,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125296923</v>
+        <v>125299459</v>
       </c>
       <c r="B22" t="n">
         <v>57513</v>
@@ -3090,14 +3095,14 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589642</v>
+        <v>589543</v>
       </c>
       <c r="R22" t="n">
-        <v>6932043</v>
+        <v>6931727</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3129,7 +3134,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3139,12 +3144,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3159,22 +3164,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125295640</v>
+        <v>125296955</v>
       </c>
       <c r="B23" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3187,27 +3192,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3216,10 +3221,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589461</v>
+        <v>589631</v>
       </c>
       <c r="R23" t="n">
-        <v>6932074</v>
+        <v>6932054</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3251,7 +3256,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3261,7 +3266,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3288,10 +3298,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125297753</v>
+        <v>125296711</v>
       </c>
       <c r="B24" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3304,39 +3314,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589545</v>
+        <v>589389</v>
       </c>
       <c r="R24" t="n">
-        <v>6931796</v>
+        <v>6931877</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3368,7 +3373,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3378,12 +3383,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3410,7 +3410,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125297742</v>
+        <v>125295328</v>
       </c>
       <c r="B25" t="n">
         <v>57513</v>
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589316</v>
+        <v>589415</v>
       </c>
       <c r="R25" t="n">
-        <v>6931994</v>
+        <v>6932018</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">

--- a/artfynd/A 9566-2025 artfynd.xlsx
+++ b/artfynd/A 9566-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125296849</v>
+        <v>125297670</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589642</v>
+        <v>589347</v>
       </c>
       <c r="R2" t="n">
-        <v>6932043</v>
+        <v>6932010</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125299074</v>
+        <v>125298021</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,31 +809,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589570</v>
+        <v>589552</v>
       </c>
       <c r="R3" t="n">
-        <v>6931668</v>
+        <v>6931786</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +887,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Misstänkt natt träd</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125296571</v>
+        <v>125296789</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>96979</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,38 +931,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589603</v>
+        <v>589642</v>
       </c>
       <c r="R4" t="n">
-        <v>6931964</v>
+        <v>6932043</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125296301</v>
+        <v>125296182</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,16 +1047,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1066,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589577</v>
+        <v>589542</v>
       </c>
       <c r="R5" t="n">
-        <v>6932028</v>
+        <v>6932034</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:49</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125297742</v>
+        <v>125296618</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,16 +1164,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1188,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589316</v>
+        <v>589671</v>
       </c>
       <c r="R6" t="n">
-        <v>6931994</v>
+        <v>6931998</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,7 +1228,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,12 +1238,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,7 +1265,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125297670</v>
+        <v>125296955</v>
       </c>
       <c r="B7" t="n">
         <v>57513</v>
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589347</v>
+        <v>589631</v>
       </c>
       <c r="R7" t="n">
-        <v>6932010</v>
+        <v>6932054</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1387,10 +1387,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125296740</v>
+        <v>125299639</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,39 +1403,48 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589642</v>
+        <v>589495</v>
       </c>
       <c r="R8" t="n">
-        <v>6932043</v>
+        <v>6931745</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1467,7 +1476,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1477,12 +1486,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:13</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,22 +1501,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125301710</v>
+        <v>125296711</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1525,39 +1529,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589415</v>
+        <v>589389</v>
       </c>
       <c r="R9" t="n">
-        <v>6931910</v>
+        <v>6931877</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1589,7 +1588,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1599,12 +1598,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>20:04</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Trummande tretå.</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1619,22 +1613,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125297600</v>
+        <v>125297753</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1647,34 +1641,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589363</v>
+        <v>589545</v>
       </c>
       <c r="R10" t="n">
-        <v>6932050</v>
+        <v>6931796</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1706,7 +1705,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1716,7 +1715,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1731,22 +1735,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125299018</v>
+        <v>125298189</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1759,27 +1763,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1788,10 +1792,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589580</v>
+        <v>589559</v>
       </c>
       <c r="R11" t="n">
-        <v>6931659</v>
+        <v>6931779</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1823,7 +1827,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1833,7 +1837,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1860,10 +1869,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125296182</v>
+        <v>125297742</v>
       </c>
       <c r="B12" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1876,16 +1885,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1905,10 +1914,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589542</v>
+        <v>589316</v>
       </c>
       <c r="R12" t="n">
-        <v>6932034</v>
+        <v>6931994</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1940,7 +1949,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1950,7 +1959,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1977,10 +1991,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125295640</v>
+        <v>125296740</v>
       </c>
       <c r="B13" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1993,27 +2007,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2022,10 +2036,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589461</v>
+        <v>589642</v>
       </c>
       <c r="R13" t="n">
-        <v>6932074</v>
+        <v>6932043</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2057,7 +2071,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2067,7 +2081,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2094,10 +2113,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125296618</v>
+        <v>125296571</v>
       </c>
       <c r="B14" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2110,39 +2129,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589671</v>
+        <v>589603</v>
       </c>
       <c r="R14" t="n">
-        <v>6931998</v>
+        <v>6931964</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2174,7 +2188,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2184,7 +2198,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2211,10 +2225,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125295606</v>
+        <v>125301710</v>
       </c>
       <c r="B15" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2223,31 +2237,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2256,10 +2270,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589420</v>
+        <v>589415</v>
       </c>
       <c r="R15" t="n">
-        <v>6932027</v>
+        <v>6931910</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2291,7 +2305,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2301,7 +2315,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>20:04</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Trummande tretå.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2328,10 +2347,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125299639</v>
+        <v>125296301</v>
       </c>
       <c r="B16" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2344,48 +2363,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589495</v>
+        <v>589577</v>
       </c>
       <c r="R16" t="n">
-        <v>6931745</v>
+        <v>6932028</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2417,7 +2427,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2427,7 +2437,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2442,12 +2457,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2576,10 +2591,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125296789</v>
+        <v>125295640</v>
       </c>
       <c r="B18" t="n">
-        <v>96979</v>
+        <v>57666</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2588,38 +2603,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589642</v>
+        <v>589461</v>
       </c>
       <c r="R18" t="n">
-        <v>6932043</v>
+        <v>6932074</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2651,7 +2671,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2661,7 +2681,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2810,10 +2830,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125298114</v>
+        <v>125296849</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2826,39 +2846,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589559</v>
+        <v>589642</v>
       </c>
       <c r="R20" t="n">
-        <v>6931779</v>
+        <v>6932043</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2890,7 +2905,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2900,12 +2915,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:03</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2920,22 +2930,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125297753</v>
+        <v>125299074</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2944,31 +2954,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2977,10 +2987,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589545</v>
+        <v>589570</v>
       </c>
       <c r="R21" t="n">
-        <v>6931796</v>
+        <v>6931668</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3012,7 +3022,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3022,12 +3032,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Misstänkt natt träd</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3176,10 +3186,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125296955</v>
+        <v>125299018</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3192,39 +3202,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589631</v>
+        <v>589580</v>
       </c>
       <c r="R23" t="n">
-        <v>6932054</v>
+        <v>6931659</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3256,7 +3266,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3266,12 +3276,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:23</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3286,19 +3291,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125296711</v>
+        <v>125297600</v>
       </c>
       <c r="B24" t="n">
         <v>78810</v>
@@ -3334,14 +3339,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589389</v>
+        <v>589363</v>
       </c>
       <c r="R24" t="n">
-        <v>6931877</v>
+        <v>6932050</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3373,7 +3378,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3383,7 +3388,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3398,12 +3403,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3532,10 +3537,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125298021</v>
+        <v>125295606</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3544,43 +3549,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589552</v>
+        <v>589420</v>
       </c>
       <c r="R26" t="n">
-        <v>6931786</v>
+        <v>6932027</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3612,7 +3617,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3622,12 +3627,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3642,12 +3642,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 9566-2025 artfynd.xlsx
+++ b/artfynd/A 9566-2025 artfynd.xlsx
@@ -1265,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125296955</v>
+        <v>125299639</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,39 +1281,48 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589631</v>
+        <v>589495</v>
       </c>
       <c r="R7" t="n">
-        <v>6932054</v>
+        <v>6931745</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,12 +1364,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:23</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,22 +1379,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125299639</v>
+        <v>125296955</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,48 +1407,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589495</v>
+        <v>589631</v>
       </c>
       <c r="R8" t="n">
-        <v>6931745</v>
+        <v>6932054</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,7 +1471,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,7 +1481,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1501,22 +1501,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125296711</v>
+        <v>125297753</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1529,34 +1529,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589389</v>
+        <v>589545</v>
       </c>
       <c r="R9" t="n">
-        <v>6931877</v>
+        <v>6931796</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1588,7 +1593,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1598,7 +1603,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1625,7 +1635,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125297753</v>
+        <v>125298189</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1670,10 +1680,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589545</v>
+        <v>589559</v>
       </c>
       <c r="R10" t="n">
-        <v>6931796</v>
+        <v>6931779</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1705,7 +1715,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1715,7 +1725,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1747,10 +1757,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125298189</v>
+        <v>125296711</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1763,39 +1773,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589559</v>
+        <v>589389</v>
       </c>
       <c r="R11" t="n">
-        <v>6931779</v>
+        <v>6931877</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1827,7 +1832,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1837,12 +1842,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2708,10 +2708,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125297544</v>
+        <v>125296849</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2724,39 +2724,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589525</v>
+        <v>589642</v>
       </c>
       <c r="R19" t="n">
-        <v>6931804</v>
+        <v>6932043</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2788,7 +2783,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2798,12 +2793,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:43</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2818,22 +2808,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125296849</v>
+        <v>125297544</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2846,34 +2836,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589642</v>
+        <v>589525</v>
       </c>
       <c r="R20" t="n">
-        <v>6932043</v>
+        <v>6931804</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2905,7 +2900,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2915,7 +2910,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2930,22 +2930,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125299074</v>
+        <v>125299459</v>
       </c>
       <c r="B21" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2954,31 +2954,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589570</v>
+        <v>589543</v>
       </c>
       <c r="R21" t="n">
-        <v>6931668</v>
+        <v>6931727</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3022,7 +3022,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Misstänkt natt träd</t>
+          <t>Ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3064,10 +3064,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125299459</v>
+        <v>125299074</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3076,31 +3076,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3109,10 +3109,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589543</v>
+        <v>589570</v>
       </c>
       <c r="R22" t="n">
-        <v>6931727</v>
+        <v>6931668</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på tall</t>
+          <t>Misstänkt natt träd</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 9566-2025 artfynd.xlsx
+++ b/artfynd/A 9566-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125297670</v>
+        <v>125297656</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -711,19 +711,19 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589347</v>
+        <v>589540</v>
       </c>
       <c r="R2" t="n">
-        <v>6932010</v>
+        <v>6931801</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,12 +785,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125296789</v>
+        <v>125301710</v>
       </c>
       <c r="B4" t="n">
-        <v>96979</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,38 +931,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589642</v>
+        <v>589415</v>
       </c>
       <c r="R4" t="n">
-        <v>6932043</v>
+        <v>6931910</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +1009,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>20:04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Trummande tretå.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125296182</v>
+        <v>125299018</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>57666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,39 +1057,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589542</v>
+        <v>589580</v>
       </c>
       <c r="R5" t="n">
-        <v>6932034</v>
+        <v>6931659</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1131,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,22 +1146,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125296618</v>
+        <v>125296740</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,16 +1174,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1193,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589671</v>
+        <v>589642</v>
       </c>
       <c r="R6" t="n">
-        <v>6931998</v>
+        <v>6932043</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,7 +1238,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1238,7 +1248,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125299639</v>
+        <v>125297544</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,36 +1296,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1319,10 +1325,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589495</v>
+        <v>589525</v>
       </c>
       <c r="R7" t="n">
-        <v>6931745</v>
+        <v>6931804</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1354,7 +1360,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,7 +1370,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1391,7 +1402,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125296955</v>
+        <v>125295328</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1436,10 +1447,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589631</v>
+        <v>589415</v>
       </c>
       <c r="R8" t="n">
-        <v>6932054</v>
+        <v>6932018</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1471,7 +1482,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1481,7 +1492,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1513,10 +1524,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125297753</v>
+        <v>125296789</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>96979</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1525,43 +1536,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589545</v>
+        <v>589642</v>
       </c>
       <c r="R9" t="n">
-        <v>6931796</v>
+        <v>6932043</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1593,7 +1599,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1603,12 +1609,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1623,22 +1624,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125298189</v>
+        <v>125296571</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1651,39 +1652,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589559</v>
+        <v>589603</v>
       </c>
       <c r="R10" t="n">
-        <v>6931779</v>
+        <v>6931964</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1715,7 +1711,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1725,12 +1721,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1745,22 +1736,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125296711</v>
+        <v>125296301</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1773,34 +1764,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589389</v>
+        <v>589577</v>
       </c>
       <c r="R11" t="n">
-        <v>6931877</v>
+        <v>6932028</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1832,7 +1828,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1842,7 +1838,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1857,22 +1858,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125297742</v>
+        <v>125299074</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1881,43 +1882,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589316</v>
+        <v>589570</v>
       </c>
       <c r="R12" t="n">
-        <v>6931994</v>
+        <v>6931668</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1949,7 +1950,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1959,12 +1960,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Misstänkt natt träd</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1979,22 +1980,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125296740</v>
+        <v>125296711</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2007,39 +2008,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589642</v>
+        <v>589389</v>
       </c>
       <c r="R13" t="n">
-        <v>6932043</v>
+        <v>6931877</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2084,11 +2080,6 @@
           <t>17:13</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2101,22 +2092,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125296571</v>
+        <v>125297670</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2129,34 +2120,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589603</v>
+        <v>589347</v>
       </c>
       <c r="R14" t="n">
-        <v>6931964</v>
+        <v>6932010</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2188,7 +2184,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2198,7 +2194,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2225,10 +2226,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125301710</v>
+        <v>125295606</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2237,31 +2238,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2270,10 +2271,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589415</v>
+        <v>589420</v>
       </c>
       <c r="R15" t="n">
-        <v>6931910</v>
+        <v>6932027</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2305,7 +2306,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2315,12 +2316,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>20:04</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Trummande tretå.</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2347,10 +2343,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125296301</v>
+        <v>125296182</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2363,16 +2359,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2392,10 +2388,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589577</v>
+        <v>589542</v>
       </c>
       <c r="R16" t="n">
-        <v>6932028</v>
+        <v>6932034</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2427,7 +2423,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2437,12 +2433,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:49</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2469,10 +2460,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125297656</v>
+        <v>125296618</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2485,16 +2476,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2505,19 +2496,19 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589540</v>
+        <v>589671</v>
       </c>
       <c r="R17" t="n">
-        <v>6931801</v>
+        <v>6931998</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2549,7 +2540,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2559,12 +2550,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2579,22 +2565,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125295640</v>
+        <v>125298189</v>
       </c>
       <c r="B18" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2607,39 +2593,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589461</v>
+        <v>589559</v>
       </c>
       <c r="R18" t="n">
-        <v>6932074</v>
+        <v>6931779</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2671,7 +2657,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2681,7 +2667,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>18:06</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2696,22 +2687,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125296849</v>
+        <v>125297742</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2724,34 +2715,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589642</v>
+        <v>589316</v>
       </c>
       <c r="R19" t="n">
-        <v>6932043</v>
+        <v>6931994</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2783,7 +2779,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2793,7 +2789,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2820,7 +2821,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125297544</v>
+        <v>125299459</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2856,7 +2857,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2865,10 +2866,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589525</v>
+        <v>589543</v>
       </c>
       <c r="R20" t="n">
-        <v>6931804</v>
+        <v>6931727</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2900,7 +2901,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2910,12 +2911,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2942,10 +2943,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125299459</v>
+        <v>125299639</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2958,27 +2959,36 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2987,10 +2997,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589543</v>
+        <v>589495</v>
       </c>
       <c r="R21" t="n">
-        <v>6931727</v>
+        <v>6931745</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3022,7 +3032,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3032,12 +3042,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:51</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på tall</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3064,10 +3069,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125299074</v>
+        <v>125296849</v>
       </c>
       <c r="B22" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3076,43 +3081,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589570</v>
+        <v>589642</v>
       </c>
       <c r="R22" t="n">
-        <v>6931668</v>
+        <v>6932043</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3154,12 +3154,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:35</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Misstänkt natt träd</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3174,19 +3169,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125299018</v>
+        <v>125295640</v>
       </c>
       <c r="B23" t="n">
         <v>57666</v>
@@ -3227,14 +3222,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589580</v>
+        <v>589461</v>
       </c>
       <c r="R23" t="n">
-        <v>6931659</v>
+        <v>6932074</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3266,7 +3261,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3276,7 +3271,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3291,12 +3286,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3415,7 +3410,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125295328</v>
+        <v>125296955</v>
       </c>
       <c r="B25" t="n">
         <v>57513</v>
@@ -3460,10 +3455,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589415</v>
+        <v>589631</v>
       </c>
       <c r="R25" t="n">
-        <v>6932018</v>
+        <v>6932054</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3495,7 +3490,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3505,7 +3500,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3537,10 +3532,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125295606</v>
+        <v>125297753</v>
       </c>
       <c r="B26" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3549,43 +3544,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589420</v>
+        <v>589545</v>
       </c>
       <c r="R26" t="n">
-        <v>6932027</v>
+        <v>6931796</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3617,7 +3612,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3627,7 +3622,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3642,12 +3642,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 9566-2025 artfynd.xlsx
+++ b/artfynd/A 9566-2025 artfynd.xlsx
@@ -2343,10 +2343,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125296182</v>
+        <v>125298189</v>
       </c>
       <c r="B16" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2359,16 +2359,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2384,14 +2384,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589542</v>
+        <v>589559</v>
       </c>
       <c r="R16" t="n">
-        <v>6932034</v>
+        <v>6931779</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2433,7 +2433,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>18:06</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2448,19 +2453,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125296618</v>
+        <v>125296182</v>
       </c>
       <c r="B17" t="n">
         <v>57529</v>
@@ -2505,10 +2510,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589671</v>
+        <v>589542</v>
       </c>
       <c r="R17" t="n">
-        <v>6931998</v>
+        <v>6932034</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2540,7 +2545,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2550,7 +2555,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2577,10 +2582,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125298189</v>
+        <v>125296618</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2593,16 +2598,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2618,14 +2623,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589559</v>
+        <v>589671</v>
       </c>
       <c r="R18" t="n">
-        <v>6931779</v>
+        <v>6931998</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2657,7 +2662,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2667,12 +2672,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:06</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2687,12 +2687,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 9566-2025 artfynd.xlsx
+++ b/artfynd/A 9566-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125297656</v>
+        <v>125298114</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589540</v>
+        <v>589559</v>
       </c>
       <c r="R2" t="n">
-        <v>6931801</v>
+        <v>6931779</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -797,7 +797,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125298021</v>
+        <v>125301710</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -833,19 +833,19 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589552</v>
+        <v>589415</v>
       </c>
       <c r="R3" t="n">
-        <v>6931786</v>
+        <v>6931910</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,12 +887,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Trummande tretå.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,22 +907,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125301710</v>
+        <v>125296849</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,39 +935,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589415</v>
+        <v>589642</v>
       </c>
       <c r="R4" t="n">
-        <v>6931910</v>
+        <v>6932043</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,12 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>20:04</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Trummande tretå.</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125299018</v>
+        <v>125299074</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,31 +1043,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1086,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589580</v>
+        <v>589570</v>
       </c>
       <c r="R5" t="n">
-        <v>6931659</v>
+        <v>6931668</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,6 +1122,11 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>18:35</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Misstänkt natt träd</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,7 +1153,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125296740</v>
+        <v>125297670</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1203,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589642</v>
+        <v>589347</v>
       </c>
       <c r="R6" t="n">
-        <v>6932043</v>
+        <v>6932010</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1248,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1402,10 +1397,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125295328</v>
+        <v>125296571</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1418,39 +1413,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589415</v>
+        <v>589603</v>
       </c>
       <c r="R8" t="n">
-        <v>6932018</v>
+        <v>6931964</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1482,7 +1472,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1492,12 +1482,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:24</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1524,10 +1509,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125296789</v>
+        <v>125296618</v>
       </c>
       <c r="B9" t="n">
-        <v>96979</v>
+        <v>57529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1536,38 +1521,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589642</v>
+        <v>589671</v>
       </c>
       <c r="R9" t="n">
-        <v>6932043</v>
+        <v>6931998</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1599,7 +1589,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1609,7 +1599,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1636,10 +1626,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125296571</v>
+        <v>125299459</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1652,34 +1642,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589603</v>
+        <v>589543</v>
       </c>
       <c r="R10" t="n">
-        <v>6931964</v>
+        <v>6931727</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1711,7 +1706,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1721,7 +1716,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1736,22 +1736,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125296301</v>
+        <v>125295640</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1764,27 +1764,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589577</v>
+        <v>589461</v>
       </c>
       <c r="R11" t="n">
-        <v>6932028</v>
+        <v>6932074</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1838,12 +1838,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:49</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1870,10 +1865,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125299074</v>
+        <v>125297742</v>
       </c>
       <c r="B12" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1882,43 +1877,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589570</v>
+        <v>589316</v>
       </c>
       <c r="R12" t="n">
-        <v>6931668</v>
+        <v>6931994</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1950,7 +1945,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1960,12 +1955,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Misstänkt natt träd</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1980,22 +1975,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125296711</v>
+        <v>125296740</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2008,34 +2003,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589389</v>
+        <v>589642</v>
       </c>
       <c r="R13" t="n">
-        <v>6931877</v>
+        <v>6932043</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2080,6 +2080,11 @@
           <t>17:13</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2092,19 +2097,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125297670</v>
+        <v>125296301</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -2149,10 +2154,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589347</v>
+        <v>589577</v>
       </c>
       <c r="R14" t="n">
-        <v>6932010</v>
+        <v>6932028</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2184,7 +2189,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2194,7 +2199,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2226,10 +2231,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125295606</v>
+        <v>125296789</v>
       </c>
       <c r="B15" t="n">
-        <v>56722</v>
+        <v>96979</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2242,39 +2247,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589420</v>
+        <v>589642</v>
       </c>
       <c r="R15" t="n">
-        <v>6932027</v>
+        <v>6932043</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2343,10 +2343,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125298189</v>
+        <v>125297600</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2359,39 +2359,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589559</v>
+        <v>589363</v>
       </c>
       <c r="R16" t="n">
-        <v>6931779</v>
+        <v>6932050</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2423,7 +2418,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2433,12 +2428,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:06</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2453,22 +2443,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125296182</v>
+        <v>125296955</v>
       </c>
       <c r="B17" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2481,16 +2471,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2510,10 +2500,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589542</v>
+        <v>589631</v>
       </c>
       <c r="R17" t="n">
-        <v>6932034</v>
+        <v>6932054</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2545,7 +2535,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2555,7 +2545,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2582,10 +2577,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125296618</v>
+        <v>125297753</v>
       </c>
       <c r="B18" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2598,16 +2593,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2623,14 +2618,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589671</v>
+        <v>589545</v>
       </c>
       <c r="R18" t="n">
-        <v>6931998</v>
+        <v>6931796</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2662,7 +2657,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2672,7 +2667,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2687,19 +2687,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125297742</v>
+        <v>125297656</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2735,19 +2735,19 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589316</v>
+        <v>589540</v>
       </c>
       <c r="R19" t="n">
-        <v>6931994</v>
+        <v>6931801</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2809,22 +2809,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125299459</v>
+        <v>125296182</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2837,16 +2837,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2862,14 +2862,14 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589543</v>
+        <v>589542</v>
       </c>
       <c r="R20" t="n">
-        <v>6931727</v>
+        <v>6932034</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2911,12 +2911,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:51</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på tall</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2931,22 +2926,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125299639</v>
+        <v>125296711</v>
       </c>
       <c r="B21" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2959,48 +2954,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589495</v>
+        <v>589389</v>
       </c>
       <c r="R21" t="n">
-        <v>6931745</v>
+        <v>6931877</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3032,7 +3013,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3042,7 +3023,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3069,10 +3050,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125296849</v>
+        <v>125295328</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3085,34 +3066,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589642</v>
+        <v>589415</v>
       </c>
       <c r="R22" t="n">
-        <v>6932043</v>
+        <v>6932018</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3144,7 +3130,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3154,7 +3140,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3181,7 +3172,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125295640</v>
+        <v>125299018</v>
       </c>
       <c r="B23" t="n">
         <v>57666</v>
@@ -3222,14 +3213,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589461</v>
+        <v>589580</v>
       </c>
       <c r="R23" t="n">
-        <v>6932074</v>
+        <v>6931659</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3261,7 +3252,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3271,7 +3262,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3286,22 +3277,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125297600</v>
+        <v>125298021</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3314,34 +3305,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589363</v>
+        <v>589552</v>
       </c>
       <c r="R24" t="n">
-        <v>6932050</v>
+        <v>6931786</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3373,7 +3369,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3383,7 +3379,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3398,22 +3399,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125296955</v>
+        <v>125295606</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3422,31 +3423,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3455,10 +3456,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589631</v>
+        <v>589420</v>
       </c>
       <c r="R25" t="n">
-        <v>6932054</v>
+        <v>6932027</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3490,7 +3491,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3500,12 +3501,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:23</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3532,10 +3528,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125297753</v>
+        <v>125299639</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3548,27 +3544,36 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3577,10 +3582,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589545</v>
+        <v>589495</v>
       </c>
       <c r="R26" t="n">
-        <v>6931796</v>
+        <v>6931745</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3612,7 +3617,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3622,12 +3627,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 9566-2025 artfynd.xlsx
+++ b/artfynd/A 9566-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125298114</v>
+        <v>125297753</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589559</v>
+        <v>589545</v>
       </c>
       <c r="R2" t="n">
-        <v>6931779</v>
+        <v>6931796</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125301710</v>
+        <v>125295328</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -845,7 +845,7 @@
         <v>589415</v>
       </c>
       <c r="R3" t="n">
-        <v>6931910</v>
+        <v>6932018</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,12 +887,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Trummande tretå.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125296849</v>
+        <v>125296923</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>57635</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,24 +935,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kångeråbäcken, Mpd</t>
@@ -994,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +1009,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125299074</v>
+        <v>125298189</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>57635</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,31 +1053,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1076,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589570</v>
+        <v>589559</v>
       </c>
       <c r="R5" t="n">
-        <v>6931668</v>
+        <v>6931779</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,12 +1131,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Misstänkt natt träd</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125297670</v>
+        <v>125296571</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>78947</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,39 +1179,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589347</v>
+        <v>589603</v>
       </c>
       <c r="R6" t="n">
-        <v>6932010</v>
+        <v>6931964</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1238,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,12 +1248,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:49</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125297544</v>
+        <v>125295606</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>56836</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,43 +1287,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589525</v>
+        <v>589420</v>
       </c>
       <c r="R7" t="n">
-        <v>6931804</v>
+        <v>6932027</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1365,12 +1365,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:43</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1385,22 +1380,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125296571</v>
+        <v>125297742</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>57635</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1413,34 +1408,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589603</v>
+        <v>589316</v>
       </c>
       <c r="R8" t="n">
-        <v>6931964</v>
+        <v>6931994</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1482,7 +1482,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1509,10 +1514,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125296618</v>
+        <v>125296301</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>57635</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1525,16 +1530,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1554,10 +1559,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589671</v>
+        <v>589577</v>
       </c>
       <c r="R9" t="n">
-        <v>6931998</v>
+        <v>6932028</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1589,7 +1594,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1599,7 +1604,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1626,10 +1636,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125299459</v>
+        <v>125297656</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1662,7 +1672,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1671,10 +1681,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589543</v>
+        <v>589540</v>
       </c>
       <c r="R10" t="n">
-        <v>6931727</v>
+        <v>6931801</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1706,7 +1716,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1716,12 +1726,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1748,10 +1758,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125295640</v>
+        <v>125301710</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>57635</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1764,21 +1774,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1793,10 +1803,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589461</v>
+        <v>589415</v>
       </c>
       <c r="R11" t="n">
-        <v>6932074</v>
+        <v>6931910</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1828,7 +1838,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1838,7 +1848,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>20:04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Trummande tretå.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1865,10 +1880,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125297742</v>
+        <v>125298021</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1906,14 +1921,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589316</v>
+        <v>589552</v>
       </c>
       <c r="R12" t="n">
-        <v>6931994</v>
+        <v>6931786</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1945,7 +1960,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1955,12 +1970,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1975,22 +1990,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125296740</v>
+        <v>125297544</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2023,19 +2038,19 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589642</v>
+        <v>589525</v>
       </c>
       <c r="R13" t="n">
-        <v>6932043</v>
+        <v>6931804</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2067,7 +2082,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2077,12 +2092,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2097,22 +2112,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125296301</v>
+        <v>125295640</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>57793</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2125,27 +2140,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2154,10 +2169,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589577</v>
+        <v>589461</v>
       </c>
       <c r="R14" t="n">
-        <v>6932028</v>
+        <v>6932074</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2189,7 +2204,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2199,12 +2214,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:49</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2231,10 +2241,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125296789</v>
+        <v>125296955</v>
       </c>
       <c r="B15" t="n">
-        <v>96979</v>
+        <v>57635</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2243,38 +2253,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589642</v>
+        <v>589631</v>
       </c>
       <c r="R15" t="n">
-        <v>6932043</v>
+        <v>6932054</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2306,7 +2321,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2316,7 +2331,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2343,10 +2363,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125297600</v>
+        <v>125296711</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2379,14 +2399,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589363</v>
+        <v>589389</v>
       </c>
       <c r="R16" t="n">
-        <v>6932050</v>
+        <v>6931877</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2418,7 +2438,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2428,7 +2448,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2443,22 +2463,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125296955</v>
+        <v>125296789</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>97147</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2467,43 +2487,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589631</v>
+        <v>589642</v>
       </c>
       <c r="R17" t="n">
-        <v>6932054</v>
+        <v>6932043</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2535,7 +2550,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2545,12 +2560,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:23</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2577,10 +2587,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125297753</v>
+        <v>125299459</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2622,10 +2632,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589545</v>
+        <v>589543</v>
       </c>
       <c r="R18" t="n">
-        <v>6931796</v>
+        <v>6931727</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2657,7 +2667,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2667,12 +2677,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2699,10 +2709,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125297656</v>
+        <v>125299639</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>57793</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2715,27 +2725,36 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2744,10 +2763,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589540</v>
+        <v>589495</v>
       </c>
       <c r="R19" t="n">
-        <v>6931801</v>
+        <v>6931745</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2779,7 +2798,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2789,12 +2808,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2821,10 +2835,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125296182</v>
+        <v>125297670</v>
       </c>
       <c r="B20" t="n">
-        <v>57529</v>
+        <v>57635</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2837,16 +2851,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2866,10 +2880,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589542</v>
+        <v>589347</v>
       </c>
       <c r="R20" t="n">
-        <v>6932034</v>
+        <v>6932010</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2901,7 +2915,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2911,7 +2925,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2938,10 +2957,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125296711</v>
+        <v>125296618</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>57632</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2954,34 +2973,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589389</v>
+        <v>589671</v>
       </c>
       <c r="R21" t="n">
-        <v>6931877</v>
+        <v>6931998</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3013,7 +3037,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3023,7 +3047,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3038,22 +3062,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125295328</v>
+        <v>125299074</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>56836</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3062,43 +3086,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589415</v>
+        <v>589570</v>
       </c>
       <c r="R22" t="n">
-        <v>6932018</v>
+        <v>6931668</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3130,7 +3154,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3140,12 +3164,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Misstänkt natt träd</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3160,22 +3184,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125299018</v>
+        <v>125297600</v>
       </c>
       <c r="B23" t="n">
-        <v>57666</v>
+        <v>78947</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3188,39 +3212,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589580</v>
+        <v>589363</v>
       </c>
       <c r="R23" t="n">
-        <v>6931659</v>
+        <v>6932050</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3252,7 +3271,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3262,7 +3281,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3277,22 +3296,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125298021</v>
+        <v>125296849</v>
       </c>
       <c r="B24" t="n">
-        <v>57513</v>
+        <v>78947</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3305,39 +3324,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589552</v>
+        <v>589642</v>
       </c>
       <c r="R24" t="n">
-        <v>6931786</v>
+        <v>6932043</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3369,7 +3383,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3379,12 +3393,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3399,22 +3408,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125295606</v>
+        <v>125299018</v>
       </c>
       <c r="B25" t="n">
-        <v>56722</v>
+        <v>57793</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3423,43 +3432,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589420</v>
+        <v>589580</v>
       </c>
       <c r="R25" t="n">
-        <v>6932027</v>
+        <v>6931659</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3491,7 +3500,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3501,7 +3510,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3516,22 +3525,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125299639</v>
+        <v>125296182</v>
       </c>
       <c r="B26" t="n">
-        <v>57666</v>
+        <v>57632</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3544,48 +3553,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589495</v>
+        <v>589542</v>
       </c>
       <c r="R26" t="n">
-        <v>6931745</v>
+        <v>6932034</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3642,12 +3642,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 9566-2025 artfynd.xlsx
+++ b/artfynd/A 9566-2025 artfynd.xlsx
@@ -1163,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125296571</v>
+        <v>125295606</v>
       </c>
       <c r="B6" t="n">
-        <v>78947</v>
+        <v>56836</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,38 +1175,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589603</v>
+        <v>589420</v>
       </c>
       <c r="R6" t="n">
-        <v>6931964</v>
+        <v>6932027</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1248,7 +1253,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125295606</v>
+        <v>125296571</v>
       </c>
       <c r="B7" t="n">
-        <v>56836</v>
+        <v>78947</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,43 +1292,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589420</v>
+        <v>589603</v>
       </c>
       <c r="R7" t="n">
-        <v>6932027</v>
+        <v>6931964</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 9566-2025 artfynd.xlsx
+++ b/artfynd/A 9566-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125297753</v>
+        <v>125296711</v>
       </c>
       <c r="B2" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589545</v>
+        <v>589389</v>
       </c>
       <c r="R2" t="n">
-        <v>6931796</v>
+        <v>6931877</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125295328</v>
+        <v>125297544</v>
       </c>
       <c r="B3" t="n">
         <v>57635</v>
@@ -833,19 +823,19 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589415</v>
+        <v>589525</v>
       </c>
       <c r="R3" t="n">
-        <v>6932018</v>
+        <v>6931804</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,19 +897,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125296923</v>
+        <v>125295328</v>
       </c>
       <c r="B4" t="n">
         <v>57635</v>
@@ -964,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589642</v>
+        <v>589415</v>
       </c>
       <c r="R4" t="n">
-        <v>6932043</v>
+        <v>6932018</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1041,7 +1031,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125298189</v>
+        <v>125296740</v>
       </c>
       <c r="B5" t="n">
         <v>57635</v>
@@ -1082,14 +1072,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589559</v>
+        <v>589642</v>
       </c>
       <c r="R5" t="n">
-        <v>6931779</v>
+        <v>6932043</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,12 +1121,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,22 +1141,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125295606</v>
+        <v>125296618</v>
       </c>
       <c r="B6" t="n">
-        <v>56836</v>
+        <v>57632</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,31 +1165,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1208,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589420</v>
+        <v>589671</v>
       </c>
       <c r="R6" t="n">
-        <v>6932027</v>
+        <v>6931998</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125296571</v>
+        <v>125299018</v>
       </c>
       <c r="B7" t="n">
-        <v>78947</v>
+        <v>57793</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1296,34 +1286,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589603</v>
+        <v>589580</v>
       </c>
       <c r="R7" t="n">
-        <v>6931964</v>
+        <v>6931659</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,7 +1350,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1365,7 +1360,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1380,22 +1375,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125297742</v>
+        <v>125296789</v>
       </c>
       <c r="B8" t="n">
-        <v>57635</v>
+        <v>97147</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1404,43 +1399,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589316</v>
+        <v>589642</v>
       </c>
       <c r="R8" t="n">
-        <v>6931994</v>
+        <v>6932043</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1472,7 +1462,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1482,12 +1472,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1514,7 +1499,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125296301</v>
+        <v>125298114</v>
       </c>
       <c r="B9" t="n">
         <v>57635</v>
@@ -1555,14 +1540,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589577</v>
+        <v>589559</v>
       </c>
       <c r="R9" t="n">
-        <v>6932028</v>
+        <v>6931779</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1594,7 +1579,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1604,12 +1589,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1624,19 +1609,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125297656</v>
+        <v>125299459</v>
       </c>
       <c r="B10" t="n">
         <v>57635</v>
@@ -1672,7 +1657,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1681,10 +1666,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589540</v>
+        <v>589543</v>
       </c>
       <c r="R10" t="n">
-        <v>6931801</v>
+        <v>6931727</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1716,7 +1701,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1726,12 +1711,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1758,10 +1743,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125301710</v>
+        <v>125299639</v>
       </c>
       <c r="B11" t="n">
-        <v>57635</v>
+        <v>57793</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1774,24 +1759,33 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
@@ -1799,14 +1793,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589415</v>
+        <v>589495</v>
       </c>
       <c r="R11" t="n">
-        <v>6931910</v>
+        <v>6931745</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1838,7 +1832,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1848,12 +1842,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>20:04</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Trummande tretå.</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1868,22 +1857,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125298021</v>
+        <v>125296849</v>
       </c>
       <c r="B12" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1896,39 +1885,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589552</v>
+        <v>589642</v>
       </c>
       <c r="R12" t="n">
-        <v>6931786</v>
+        <v>6932043</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1960,7 +1944,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1970,12 +1954,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1990,19 +1969,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125297544</v>
+        <v>125296301</v>
       </c>
       <c r="B13" t="n">
         <v>57635</v>
@@ -2038,19 +2017,19 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589525</v>
+        <v>589577</v>
       </c>
       <c r="R13" t="n">
-        <v>6931804</v>
+        <v>6932028</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2082,7 +2061,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2092,12 +2071,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2112,22 +2091,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125295640</v>
+        <v>125296955</v>
       </c>
       <c r="B14" t="n">
-        <v>57793</v>
+        <v>57635</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2140,27 +2119,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2169,10 +2148,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589461</v>
+        <v>589631</v>
       </c>
       <c r="R14" t="n">
-        <v>6932074</v>
+        <v>6932054</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2204,7 +2183,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2214,7 +2193,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2241,10 +2225,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125296955</v>
+        <v>125297600</v>
       </c>
       <c r="B15" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2257,39 +2241,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589631</v>
+        <v>589363</v>
       </c>
       <c r="R15" t="n">
-        <v>6932054</v>
+        <v>6932050</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2321,7 +2300,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2331,12 +2310,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:23</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2363,10 +2337,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125296711</v>
+        <v>125297670</v>
       </c>
       <c r="B16" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2379,34 +2353,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589389</v>
+        <v>589347</v>
       </c>
       <c r="R16" t="n">
-        <v>6931877</v>
+        <v>6932010</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2438,7 +2417,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2448,7 +2427,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2463,22 +2447,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125296789</v>
+        <v>125296571</v>
       </c>
       <c r="B17" t="n">
-        <v>97147</v>
+        <v>78947</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2487,38 +2471,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589642</v>
+        <v>589603</v>
       </c>
       <c r="R17" t="n">
-        <v>6932043</v>
+        <v>6931964</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2550,7 +2534,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2560,7 +2544,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2587,10 +2571,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125299459</v>
+        <v>125295640</v>
       </c>
       <c r="B18" t="n">
-        <v>57635</v>
+        <v>57793</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2603,39 +2587,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589543</v>
+        <v>589461</v>
       </c>
       <c r="R18" t="n">
-        <v>6931727</v>
+        <v>6932074</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2667,7 +2651,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2677,12 +2661,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:51</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på tall</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2697,22 +2676,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125299639</v>
+        <v>125296182</v>
       </c>
       <c r="B19" t="n">
-        <v>57793</v>
+        <v>57632</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2725,48 +2704,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589495</v>
+        <v>589542</v>
       </c>
       <c r="R19" t="n">
-        <v>6931745</v>
+        <v>6932034</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2798,7 +2768,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2808,7 +2778,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2823,19 +2793,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125297670</v>
+        <v>125297753</v>
       </c>
       <c r="B20" t="n">
         <v>57635</v>
@@ -2876,14 +2846,14 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589347</v>
+        <v>589545</v>
       </c>
       <c r="R20" t="n">
-        <v>6932010</v>
+        <v>6931796</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2915,7 +2885,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2925,12 +2895,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2945,22 +2915,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125296618</v>
+        <v>125297742</v>
       </c>
       <c r="B21" t="n">
-        <v>57632</v>
+        <v>57635</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2973,16 +2943,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3002,10 +2972,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589671</v>
+        <v>589316</v>
       </c>
       <c r="R21" t="n">
-        <v>6931998</v>
+        <v>6931994</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3037,7 +3007,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3047,7 +3017,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3074,10 +3049,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125299074</v>
+        <v>125297656</v>
       </c>
       <c r="B22" t="n">
-        <v>56836</v>
+        <v>57635</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3086,31 +3061,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3119,10 +3094,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589570</v>
+        <v>589540</v>
       </c>
       <c r="R22" t="n">
-        <v>6931668</v>
+        <v>6931801</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3154,7 +3129,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3164,12 +3139,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Misstänkt natt träd</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3196,10 +3171,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125297600</v>
+        <v>125299074</v>
       </c>
       <c r="B23" t="n">
-        <v>78947</v>
+        <v>56836</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3208,38 +3183,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589363</v>
+        <v>589570</v>
       </c>
       <c r="R23" t="n">
-        <v>6932050</v>
+        <v>6931668</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3271,7 +3251,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3281,7 +3261,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Misstänkt natt träd</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3296,22 +3281,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125296849</v>
+        <v>125295606</v>
       </c>
       <c r="B24" t="n">
-        <v>78947</v>
+        <v>56836</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3320,38 +3305,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589642</v>
+        <v>589420</v>
       </c>
       <c r="R24" t="n">
-        <v>6932043</v>
+        <v>6932027</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3383,7 +3373,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3393,7 +3383,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3420,10 +3410,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125299018</v>
+        <v>125298021</v>
       </c>
       <c r="B25" t="n">
-        <v>57793</v>
+        <v>57635</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3436,27 +3426,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3465,10 +3455,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589580</v>
+        <v>589552</v>
       </c>
       <c r="R25" t="n">
-        <v>6931659</v>
+        <v>6931786</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3500,7 +3490,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3510,7 +3500,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3537,10 +3532,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125296182</v>
+        <v>125301710</v>
       </c>
       <c r="B26" t="n">
-        <v>57632</v>
+        <v>57635</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3553,16 +3548,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3573,7 +3568,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3582,10 +3577,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589542</v>
+        <v>589415</v>
       </c>
       <c r="R26" t="n">
-        <v>6932034</v>
+        <v>6931910</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3617,7 +3612,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3627,7 +3622,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>20:04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Trummande tretå.</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 9566-2025 artfynd.xlsx
+++ b/artfynd/A 9566-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125295328</v>
+        <v>125296618</v>
       </c>
       <c r="B4" t="n">
-        <v>57635</v>
+        <v>57632</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,16 +925,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589415</v>
+        <v>589671</v>
       </c>
       <c r="R4" t="n">
-        <v>6932018</v>
+        <v>6931998</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,12 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:24</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,7 +1026,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125296740</v>
+        <v>125295328</v>
       </c>
       <c r="B5" t="n">
         <v>57635</v>
@@ -1076,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589642</v>
+        <v>589415</v>
       </c>
       <c r="R5" t="n">
-        <v>6932043</v>
+        <v>6932018</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1153,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125296618</v>
+        <v>125296740</v>
       </c>
       <c r="B6" t="n">
-        <v>57632</v>
+        <v>57635</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,16 +1164,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1198,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589671</v>
+        <v>589642</v>
       </c>
       <c r="R6" t="n">
-        <v>6931998</v>
+        <v>6932043</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1228,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1238,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -2459,10 +2459,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125296571</v>
+        <v>125295640</v>
       </c>
       <c r="B17" t="n">
-        <v>78947</v>
+        <v>57793</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2475,34 +2475,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589603</v>
+        <v>589461</v>
       </c>
       <c r="R17" t="n">
-        <v>6931964</v>
+        <v>6932074</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2534,7 +2539,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2544,7 +2549,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2571,10 +2576,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125295640</v>
+        <v>125296571</v>
       </c>
       <c r="B18" t="n">
-        <v>57793</v>
+        <v>78947</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2587,39 +2592,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589461</v>
+        <v>589603</v>
       </c>
       <c r="R18" t="n">
-        <v>6932074</v>
+        <v>6931964</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 9566-2025 artfynd.xlsx
+++ b/artfynd/A 9566-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125296711</v>
+        <v>125296849</v>
       </c>
       <c r="B2" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,14 +706,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589389</v>
+        <v>589642</v>
       </c>
       <c r="R2" t="n">
-        <v>6931877</v>
+        <v>6932043</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,67 +770,62 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125297544</v>
+        <v>125295606</v>
       </c>
       <c r="B3" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589525</v>
+        <v>589420</v>
       </c>
       <c r="R3" t="n">
-        <v>6931804</v>
+        <v>6932027</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:43</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,27 +882,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125296618</v>
+        <v>125296955</v>
       </c>
       <c r="B4" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,16 +905,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -954,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589671</v>
+        <v>589631</v>
       </c>
       <c r="R4" t="n">
-        <v>6931998</v>
+        <v>6932054</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,15 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125295328</v>
+        <v>125297742</v>
       </c>
       <c r="B5" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589415</v>
+        <v>589316</v>
       </c>
       <c r="R5" t="n">
-        <v>6932018</v>
+        <v>6931994</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1148,15 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125296740</v>
+        <v>125297544</v>
       </c>
       <c r="B6" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,19 +1159,19 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589642</v>
+        <v>589525</v>
       </c>
       <c r="R6" t="n">
-        <v>6932043</v>
+        <v>6931804</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1238,12 +1213,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,12 +1233,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1273,12 +1248,7 @@
         <v>125299018</v>
       </c>
       <c r="B7" t="n">
-        <v>57793</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57811</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,50 +1357,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125296789</v>
+        <v>125297670</v>
       </c>
       <c r="B8" t="n">
-        <v>97147</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589642</v>
+        <v>589347</v>
       </c>
       <c r="R8" t="n">
-        <v>6932043</v>
+        <v>6932010</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1462,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1472,7 +1442,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1499,55 +1474,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125298114</v>
+        <v>125296789</v>
       </c>
       <c r="B9" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97202</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589559</v>
+        <v>589642</v>
       </c>
       <c r="R9" t="n">
-        <v>6931779</v>
+        <v>6932043</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1579,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1589,12 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:03</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1609,27 +1569,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125299459</v>
+        <v>125301710</v>
       </c>
       <c r="B10" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,19 +1612,19 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589543</v>
+        <v>589415</v>
       </c>
       <c r="R10" t="n">
-        <v>6931727</v>
+        <v>6931910</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1701,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1711,12 +1666,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på tall</t>
+          <t>Trummande tretå.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1731,64 +1686,50 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125299639</v>
+        <v>125299074</v>
       </c>
       <c r="B11" t="n">
-        <v>57793</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1797,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589495</v>
+        <v>589570</v>
       </c>
       <c r="R11" t="n">
-        <v>6931745</v>
+        <v>6931668</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1832,7 +1773,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1842,7 +1783,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Misstänkt natt träd</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1869,15 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125296849</v>
+        <v>125296711</v>
       </c>
       <c r="B12" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,14 +1846,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589642</v>
+        <v>589389</v>
       </c>
       <c r="R12" t="n">
-        <v>6932043</v>
+        <v>6931877</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1944,7 +1885,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1954,7 +1895,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1969,27 +1910,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125296301</v>
+        <v>125296618</v>
       </c>
       <c r="B13" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,16 +1933,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2026,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589577</v>
+        <v>589671</v>
       </c>
       <c r="R13" t="n">
-        <v>6932028</v>
+        <v>6931998</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2061,7 +1997,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2071,12 +2007,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:49</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2103,15 +2034,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125296955</v>
+        <v>125297600</v>
       </c>
       <c r="B14" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,39 +2045,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589631</v>
+        <v>589363</v>
       </c>
       <c r="R14" t="n">
-        <v>6932054</v>
+        <v>6932050</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2183,7 +2104,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2193,12 +2114,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:23</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2225,15 +2141,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125297600</v>
+        <v>125297656</v>
       </c>
       <c r="B15" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2241,34 +2152,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589363</v>
+        <v>589540</v>
       </c>
       <c r="R15" t="n">
-        <v>6932050</v>
+        <v>6931801</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2300,7 +2216,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2310,7 +2226,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2325,27 +2246,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125297670</v>
+        <v>125298021</v>
       </c>
       <c r="B16" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2378,14 +2294,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589347</v>
+        <v>589552</v>
       </c>
       <c r="R16" t="n">
-        <v>6932010</v>
+        <v>6931786</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2417,7 +2333,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2427,12 +2343,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2447,27 +2363,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125295640</v>
+        <v>125296923</v>
       </c>
       <c r="B17" t="n">
-        <v>57793</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,27 +2386,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2504,10 +2415,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589461</v>
+        <v>589642</v>
       </c>
       <c r="R17" t="n">
-        <v>6932074</v>
+        <v>6932043</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2539,7 +2450,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2549,7 +2460,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2576,15 +2492,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125296571</v>
+        <v>125299639</v>
       </c>
       <c r="B18" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57811</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,34 +2503,48 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589603</v>
+        <v>589495</v>
       </c>
       <c r="R18" t="n">
-        <v>6931964</v>
+        <v>6931745</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2651,7 +2576,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2661,7 +2586,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2676,12 +2601,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2691,12 +2616,7 @@
         <v>125296182</v>
       </c>
       <c r="B19" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2805,15 +2725,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125297753</v>
+        <v>125296571</v>
       </c>
       <c r="B20" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2821,39 +2736,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589545</v>
+        <v>589603</v>
       </c>
       <c r="R20" t="n">
-        <v>6931796</v>
+        <v>6931964</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2885,7 +2795,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2895,12 +2805,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2915,27 +2820,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125297742</v>
+        <v>125297753</v>
       </c>
       <c r="B21" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2968,14 +2868,14 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589316</v>
+        <v>589545</v>
       </c>
       <c r="R21" t="n">
-        <v>6931994</v>
+        <v>6931796</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3022,7 +2922,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3037,27 +2937,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125297656</v>
+        <v>125299459</v>
       </c>
       <c r="B22" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3085,7 +2980,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3094,10 +2989,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589540</v>
+        <v>589543</v>
       </c>
       <c r="R22" t="n">
-        <v>6931801</v>
+        <v>6931727</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3129,7 +3024,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3139,12 +3034,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3171,43 +3066,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125299074</v>
+        <v>125298189</v>
       </c>
       <c r="B23" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3216,10 +3106,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589570</v>
+        <v>589559</v>
       </c>
       <c r="R23" t="n">
-        <v>6931668</v>
+        <v>6931779</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3251,7 +3141,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3261,12 +3151,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Misstänkt natt träd</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3293,43 +3183,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125295606</v>
+        <v>125295328</v>
       </c>
       <c r="B24" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3338,10 +3223,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589420</v>
+        <v>589415</v>
       </c>
       <c r="R24" t="n">
-        <v>6932027</v>
+        <v>6932018</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3373,7 +3258,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3383,7 +3268,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3410,15 +3300,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125298021</v>
+        <v>125295640</v>
       </c>
       <c r="B25" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57811</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3426,39 +3311,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589552</v>
+        <v>589461</v>
       </c>
       <c r="R25" t="n">
-        <v>6931786</v>
+        <v>6932074</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3490,7 +3375,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3500,12 +3385,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3520,27 +3400,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125301710</v>
+        <v>125296301</v>
       </c>
       <c r="B26" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3568,7 +3443,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3577,10 +3452,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589415</v>
+        <v>589577</v>
       </c>
       <c r="R26" t="n">
-        <v>6931910</v>
+        <v>6932028</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3612,7 +3487,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3622,12 +3497,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Trummande tretå.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3651,6 +3526,457 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>125869409</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91220</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Palmastjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>589372</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6931951</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>125871685</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57811</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Palmastjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>589533</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6931958</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>125869414</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98324</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Kångeråbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>589371</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6931943</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>125869329</v>
+      </c>
+      <c r="B30" t="n">
+        <v>56843</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Palmastjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>589374</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6931940</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Fjäder av tjäder tupp</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9566-2025 artfynd.xlsx
+++ b/artfynd/A 9566-2025 artfynd.xlsx
@@ -782,38 +782,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125295606</v>
+        <v>125296955</v>
       </c>
       <c r="B3" t="n">
-        <v>56843</v>
+        <v>57651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589420</v>
+        <v>589631</v>
       </c>
       <c r="R3" t="n">
-        <v>6932027</v>
+        <v>6932054</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,38 +899,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125296955</v>
+        <v>125295606</v>
       </c>
       <c r="B4" t="n">
-        <v>57651</v>
+        <v>56843</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -934,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589631</v>
+        <v>589420</v>
       </c>
       <c r="R4" t="n">
-        <v>6932054</v>
+        <v>6932027</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1474,45 +1474,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125296789</v>
+        <v>125301710</v>
       </c>
       <c r="B9" t="n">
-        <v>97202</v>
+        <v>57651</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589642</v>
+        <v>589415</v>
       </c>
       <c r="R9" t="n">
-        <v>6932043</v>
+        <v>6931910</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1559,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>20:04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Trummande tretå.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,50 +1591,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125301710</v>
+        <v>125296789</v>
       </c>
       <c r="B10" t="n">
-        <v>57651</v>
+        <v>97202</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589415</v>
+        <v>589642</v>
       </c>
       <c r="R10" t="n">
-        <v>6931910</v>
+        <v>6932043</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1656,7 +1661,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,12 +1671,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>20:04</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Trummande tretå.</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 9566-2025 artfynd.xlsx
+++ b/artfynd/A 9566-2025 artfynd.xlsx
@@ -1474,50 +1474,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125301710</v>
+        <v>125296789</v>
       </c>
       <c r="B9" t="n">
-        <v>57651</v>
+        <v>97209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589415</v>
+        <v>589642</v>
       </c>
       <c r="R9" t="n">
-        <v>6931910</v>
+        <v>6932043</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1549,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,12 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>20:04</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Trummande tretå.</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,45 +1581,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125296789</v>
+        <v>125301710</v>
       </c>
       <c r="B10" t="n">
-        <v>97202</v>
+        <v>57651</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589642</v>
+        <v>589415</v>
       </c>
       <c r="R10" t="n">
-        <v>6932043</v>
+        <v>6931910</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1661,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1671,7 +1666,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>20:04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Trummande tretå.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1922,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125296618</v>
+        <v>125297600</v>
       </c>
       <c r="B13" t="n">
-        <v>57648</v>
+        <v>78967</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1933,39 +1933,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589671</v>
+        <v>589363</v>
       </c>
       <c r="R13" t="n">
-        <v>6931998</v>
+        <v>6932050</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1997,7 +1992,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2007,7 +2002,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2034,10 +2029,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125297600</v>
+        <v>125296618</v>
       </c>
       <c r="B14" t="n">
-        <v>78967</v>
+        <v>57648</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2045,34 +2040,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589363</v>
+        <v>589671</v>
       </c>
       <c r="R14" t="n">
-        <v>6932050</v>
+        <v>6931998</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2492,10 +2492,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125299639</v>
+        <v>125296182</v>
       </c>
       <c r="B18" t="n">
-        <v>57811</v>
+        <v>57648</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2503,48 +2503,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589495</v>
+        <v>589542</v>
       </c>
       <c r="R18" t="n">
-        <v>6931745</v>
+        <v>6932034</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2576,7 +2567,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2586,7 +2577,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2601,22 +2592,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125296182</v>
+        <v>125296571</v>
       </c>
       <c r="B19" t="n">
-        <v>57648</v>
+        <v>78967</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,39 +2615,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589542</v>
+        <v>589603</v>
       </c>
       <c r="R19" t="n">
-        <v>6932034</v>
+        <v>6931964</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2688,7 +2674,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2698,7 +2684,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2725,10 +2711,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125296571</v>
+        <v>125297753</v>
       </c>
       <c r="B20" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2736,34 +2722,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589603</v>
+        <v>589545</v>
       </c>
       <c r="R20" t="n">
-        <v>6931964</v>
+        <v>6931796</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2795,7 +2786,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2805,7 +2796,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2820,22 +2816,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125297753</v>
+        <v>125299639</v>
       </c>
       <c r="B21" t="n">
-        <v>57651</v>
+        <v>57811</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2843,27 +2839,36 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2872,10 +2877,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589545</v>
+        <v>589495</v>
       </c>
       <c r="R21" t="n">
-        <v>6931796</v>
+        <v>6931745</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2907,7 +2912,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2917,12 +2922,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3532,7 +3532,7 @@
         <v>125869409</v>
       </c>
       <c r="B27" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>125869414</v>
       </c>
       <c r="B29" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 9566-2025 artfynd.xlsx
+++ b/artfynd/A 9566-2025 artfynd.xlsx
@@ -1922,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125297600</v>
+        <v>125296618</v>
       </c>
       <c r="B13" t="n">
-        <v>78967</v>
+        <v>57648</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1933,34 +1933,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589363</v>
+        <v>589671</v>
       </c>
       <c r="R13" t="n">
-        <v>6932050</v>
+        <v>6931998</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1992,7 +1997,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2002,7 +2007,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,10 +2034,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125296618</v>
+        <v>125297656</v>
       </c>
       <c r="B14" t="n">
-        <v>57648</v>
+        <v>57651</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2040,16 +2045,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2060,19 +2065,19 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589671</v>
+        <v>589540</v>
       </c>
       <c r="R14" t="n">
-        <v>6931998</v>
+        <v>6931801</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2104,7 +2109,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2114,7 +2119,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2129,22 +2139,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125297656</v>
+        <v>125297600</v>
       </c>
       <c r="B15" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2152,39 +2162,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589540</v>
+        <v>589363</v>
       </c>
       <c r="R15" t="n">
-        <v>6931801</v>
+        <v>6932050</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2216,7 +2221,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2226,12 +2231,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2246,12 +2246,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2492,10 +2492,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125296182</v>
+        <v>125296571</v>
       </c>
       <c r="B18" t="n">
-        <v>57648</v>
+        <v>78967</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2503,39 +2503,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589542</v>
+        <v>589603</v>
       </c>
       <c r="R18" t="n">
-        <v>6932034</v>
+        <v>6931964</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2567,7 +2562,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2577,7 +2572,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2604,10 +2599,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125296571</v>
+        <v>125296182</v>
       </c>
       <c r="B19" t="n">
-        <v>78967</v>
+        <v>57648</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2615,34 +2610,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589603</v>
+        <v>589542</v>
       </c>
       <c r="R19" t="n">
-        <v>6931964</v>
+        <v>6932034</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3529,10 +3529,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125869409</v>
+        <v>125871685</v>
       </c>
       <c r="B27" t="n">
-        <v>91227</v>
+        <v>57811</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3540,34 +3540,43 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Palmastjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589372</v>
+        <v>589533</v>
       </c>
       <c r="R27" t="n">
-        <v>6931951</v>
+        <v>6931958</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3599,7 +3608,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3609,7 +3618,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3636,10 +3645,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125871685</v>
+        <v>125869409</v>
       </c>
       <c r="B28" t="n">
-        <v>57811</v>
+        <v>91227</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3647,43 +3656,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Palmastjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589533</v>
+        <v>589372</v>
       </c>
       <c r="R28" t="n">
-        <v>6931958</v>
+        <v>6931951</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 9566-2025 artfynd.xlsx
+++ b/artfynd/A 9566-2025 artfynd.xlsx
@@ -2492,10 +2492,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125296571</v>
+        <v>125299639</v>
       </c>
       <c r="B18" t="n">
-        <v>78967</v>
+        <v>57811</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2503,34 +2503,48 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589603</v>
+        <v>589495</v>
       </c>
       <c r="R18" t="n">
-        <v>6931964</v>
+        <v>6931745</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2562,7 +2576,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2572,7 +2586,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2587,12 +2601,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2711,10 +2725,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125297753</v>
+        <v>125296571</v>
       </c>
       <c r="B20" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2722,39 +2736,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589545</v>
+        <v>589603</v>
       </c>
       <c r="R20" t="n">
-        <v>6931796</v>
+        <v>6931964</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2786,7 +2795,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2796,12 +2805,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2816,22 +2820,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125299639</v>
+        <v>125297753</v>
       </c>
       <c r="B21" t="n">
-        <v>57811</v>
+        <v>57651</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2839,36 +2843,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2877,10 +2872,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589495</v>
+        <v>589545</v>
       </c>
       <c r="R21" t="n">
-        <v>6931745</v>
+        <v>6931796</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2912,7 +2907,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2922,7 +2917,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3529,10 +3529,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125871685</v>
+        <v>125869409</v>
       </c>
       <c r="B27" t="n">
-        <v>57811</v>
+        <v>91228</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3540,43 +3540,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Palmastjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589533</v>
+        <v>589372</v>
       </c>
       <c r="R27" t="n">
-        <v>6931958</v>
+        <v>6931951</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3608,7 +3599,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3618,7 +3609,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3645,10 +3636,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125869409</v>
+        <v>125871685</v>
       </c>
       <c r="B28" t="n">
-        <v>91227</v>
+        <v>57811</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3656,34 +3647,43 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Palmastjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589372</v>
+        <v>589533</v>
       </c>
       <c r="R28" t="n">
-        <v>6931951</v>
+        <v>6931958</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3755,7 +3755,7 @@
         <v>125869414</v>
       </c>
       <c r="B29" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 9566-2025 artfynd.xlsx
+++ b/artfynd/A 9566-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125296849</v>
       </c>
       <c r="B2" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125297742</v>
+        <v>125299018</v>
       </c>
       <c r="B5" t="n">
-        <v>57651</v>
+        <v>57811</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,39 +1022,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589316</v>
+        <v>589580</v>
       </c>
       <c r="R5" t="n">
-        <v>6931994</v>
+        <v>6931659</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,12 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,19 +1111,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125297544</v>
+        <v>125297742</v>
       </c>
       <c r="B6" t="n">
         <v>57651</v>
@@ -1159,19 +1154,19 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589525</v>
+        <v>589316</v>
       </c>
       <c r="R6" t="n">
-        <v>6931804</v>
+        <v>6931994</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,12 +1208,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,22 +1228,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125299018</v>
+        <v>125297544</v>
       </c>
       <c r="B7" t="n">
-        <v>57811</v>
+        <v>57651</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,27 +1251,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1285,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589580</v>
+        <v>589525</v>
       </c>
       <c r="R7" t="n">
-        <v>6931659</v>
+        <v>6931804</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1325,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1474,45 +1474,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125296789</v>
+        <v>125301710</v>
       </c>
       <c r="B9" t="n">
-        <v>97209</v>
+        <v>57651</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589642</v>
+        <v>589415</v>
       </c>
       <c r="R9" t="n">
-        <v>6932043</v>
+        <v>6931910</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1559,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>20:04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Trummande tretå.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,50 +1591,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125301710</v>
+        <v>125296789</v>
       </c>
       <c r="B10" t="n">
-        <v>57651</v>
+        <v>97212</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589415</v>
+        <v>589642</v>
       </c>
       <c r="R10" t="n">
-        <v>6931910</v>
+        <v>6932043</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1656,7 +1661,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,12 +1671,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>20:04</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Trummande tretå.</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1818,7 +1818,7 @@
         <v>125296711</v>
       </c>
       <c r="B12" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1922,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125296618</v>
+        <v>125297656</v>
       </c>
       <c r="B13" t="n">
-        <v>57648</v>
+        <v>57651</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1933,16 +1933,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1953,19 +1953,19 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589671</v>
+        <v>589540</v>
       </c>
       <c r="R13" t="n">
-        <v>6931998</v>
+        <v>6931801</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2007,7 +2007,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2022,22 +2027,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125297656</v>
+        <v>125296618</v>
       </c>
       <c r="B14" t="n">
-        <v>57651</v>
+        <v>57648</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2045,16 +2050,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2065,19 +2070,19 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589540</v>
+        <v>589671</v>
       </c>
       <c r="R14" t="n">
-        <v>6931801</v>
+        <v>6931998</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2109,7 +2114,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2119,12 +2124,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2139,12 +2139,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2154,7 +2154,7 @@
         <v>125297600</v>
       </c>
       <c r="B15" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2492,10 +2492,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125299639</v>
+        <v>125297753</v>
       </c>
       <c r="B18" t="n">
-        <v>57811</v>
+        <v>57651</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2503,36 +2503,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2541,10 +2532,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589495</v>
+        <v>589545</v>
       </c>
       <c r="R18" t="n">
-        <v>6931745</v>
+        <v>6931796</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2576,7 +2567,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2586,7 +2577,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2728,7 +2724,7 @@
         <v>125296571</v>
       </c>
       <c r="B20" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2832,10 +2828,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125297753</v>
+        <v>125299639</v>
       </c>
       <c r="B21" t="n">
-        <v>57651</v>
+        <v>57811</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2843,27 +2839,36 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2872,10 +2877,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589545</v>
+        <v>589495</v>
       </c>
       <c r="R21" t="n">
-        <v>6931796</v>
+        <v>6931745</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2907,7 +2912,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2917,12 +2922,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3755,7 +3755,7 @@
         <v>125869414</v>
       </c>
       <c r="B29" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 9566-2025 artfynd.xlsx
+++ b/artfynd/A 9566-2025 artfynd.xlsx
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125299018</v>
+        <v>125297742</v>
       </c>
       <c r="B5" t="n">
-        <v>57811</v>
+        <v>57651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,39 +1022,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589580</v>
+        <v>589316</v>
       </c>
       <c r="R5" t="n">
-        <v>6931659</v>
+        <v>6931994</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,19 +1116,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125297742</v>
+        <v>125297544</v>
       </c>
       <c r="B6" t="n">
         <v>57651</v>
@@ -1154,19 +1159,19 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589316</v>
+        <v>589525</v>
       </c>
       <c r="R6" t="n">
-        <v>6931994</v>
+        <v>6931804</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,12 +1213,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,22 +1233,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125297544</v>
+        <v>125299018</v>
       </c>
       <c r="B7" t="n">
-        <v>57651</v>
+        <v>57811</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,27 +1256,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1280,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589525</v>
+        <v>589580</v>
       </c>
       <c r="R7" t="n">
-        <v>6931804</v>
+        <v>6931659</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,12 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:43</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -2492,10 +2492,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125297753</v>
+        <v>125296182</v>
       </c>
       <c r="B18" t="n">
-        <v>57651</v>
+        <v>57648</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2503,16 +2503,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2528,14 +2528,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589545</v>
+        <v>589542</v>
       </c>
       <c r="R18" t="n">
-        <v>6931796</v>
+        <v>6932034</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2577,12 +2577,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2597,22 +2592,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125296182</v>
+        <v>125296571</v>
       </c>
       <c r="B19" t="n">
-        <v>57648</v>
+        <v>78968</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2620,39 +2615,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589542</v>
+        <v>589603</v>
       </c>
       <c r="R19" t="n">
-        <v>6932034</v>
+        <v>6931964</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2684,7 +2674,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2694,7 +2684,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2721,10 +2711,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125296571</v>
+        <v>125297753</v>
       </c>
       <c r="B20" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2732,34 +2722,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589603</v>
+        <v>589545</v>
       </c>
       <c r="R20" t="n">
-        <v>6931964</v>
+        <v>6931796</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2791,7 +2786,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2801,7 +2796,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2816,12 +2816,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 9566-2025 artfynd.xlsx
+++ b/artfynd/A 9566-2025 artfynd.xlsx
@@ -3532,7 +3532,7 @@
         <v>125869409</v>
       </c>
       <c r="B27" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>125869414</v>
       </c>
       <c r="B29" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 9566-2025 artfynd.xlsx
+++ b/artfynd/A 9566-2025 artfynd.xlsx
@@ -3755,7 +3755,7 @@
         <v>125869414</v>
       </c>
       <c r="B29" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 9566-2025 artfynd.xlsx
+++ b/artfynd/A 9566-2025 artfynd.xlsx
@@ -3532,7 +3532,7 @@
         <v>125869409</v>
       </c>
       <c r="B27" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>125871685</v>
       </c>
       <c r="B28" t="n">
-        <v>57811</v>
+        <v>57812</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>125869414</v>
       </c>
       <c r="B29" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>125869329</v>
       </c>
       <c r="B30" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 9566-2025 artfynd.xlsx
+++ b/artfynd/A 9566-2025 artfynd.xlsx
@@ -3529,10 +3529,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125869409</v>
+        <v>125871685</v>
       </c>
       <c r="B27" t="n">
-        <v>91234</v>
+        <v>57812</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3540,34 +3540,43 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Palmastjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589372</v>
+        <v>589533</v>
       </c>
       <c r="R27" t="n">
-        <v>6931951</v>
+        <v>6931958</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3599,7 +3608,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3609,7 +3618,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3636,10 +3645,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125871685</v>
+        <v>125869409</v>
       </c>
       <c r="B28" t="n">
-        <v>57812</v>
+        <v>91236</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3647,43 +3656,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Palmastjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589533</v>
+        <v>589372</v>
       </c>
       <c r="R28" t="n">
-        <v>6931958</v>
+        <v>6931951</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3755,7 +3755,7 @@
         <v>125869414</v>
       </c>
       <c r="B29" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 9566-2025 artfynd.xlsx
+++ b/artfynd/A 9566-2025 artfynd.xlsx
@@ -3529,10 +3529,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125871685</v>
+        <v>125869409</v>
       </c>
       <c r="B27" t="n">
-        <v>57812</v>
+        <v>91236</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3540,43 +3540,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Palmastjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589533</v>
+        <v>589372</v>
       </c>
       <c r="R27" t="n">
-        <v>6931958</v>
+        <v>6931951</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3608,7 +3599,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3618,7 +3609,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3645,10 +3636,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125869409</v>
+        <v>125871685</v>
       </c>
       <c r="B28" t="n">
-        <v>91236</v>
+        <v>57812</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3656,34 +3647,43 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Palmastjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589372</v>
+        <v>589533</v>
       </c>
       <c r="R28" t="n">
-        <v>6931951</v>
+        <v>6931958</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 9566-2025 artfynd.xlsx
+++ b/artfynd/A 9566-2025 artfynd.xlsx
@@ -3532,7 +3532,7 @@
         <v>125869409</v>
       </c>
       <c r="B27" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>125869414</v>
       </c>
       <c r="B29" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 9566-2025 artfynd.xlsx
+++ b/artfynd/A 9566-2025 artfynd.xlsx
@@ -3529,10 +3529,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125869409</v>
+        <v>125871685</v>
       </c>
       <c r="B27" t="n">
-        <v>91238</v>
+        <v>57816</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3540,34 +3540,43 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Palmastjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589372</v>
+        <v>589533</v>
       </c>
       <c r="R27" t="n">
-        <v>6931951</v>
+        <v>6931958</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3599,7 +3608,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3609,7 +3618,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3636,10 +3645,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125871685</v>
+        <v>125869409</v>
       </c>
       <c r="B28" t="n">
-        <v>57812</v>
+        <v>91242</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3647,43 +3656,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Palmastjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589533</v>
+        <v>589372</v>
       </c>
       <c r="R28" t="n">
-        <v>6931958</v>
+        <v>6931951</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3755,7 +3755,7 @@
         <v>125869414</v>
       </c>
       <c r="B29" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>125869329</v>
       </c>
       <c r="B30" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 9566-2025 artfynd.xlsx
+++ b/artfynd/A 9566-2025 artfynd.xlsx
@@ -3529,10 +3529,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125871685</v>
+        <v>125869409</v>
       </c>
       <c r="B27" t="n">
-        <v>57816</v>
+        <v>91242</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3540,43 +3540,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Palmastjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589533</v>
+        <v>589372</v>
       </c>
       <c r="R27" t="n">
-        <v>6931958</v>
+        <v>6931951</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3608,7 +3599,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3618,7 +3609,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3645,10 +3636,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125869409</v>
+        <v>125871685</v>
       </c>
       <c r="B28" t="n">
-        <v>91242</v>
+        <v>57816</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3656,34 +3647,43 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Palmastjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589372</v>
+        <v>589533</v>
       </c>
       <c r="R28" t="n">
-        <v>6931951</v>
+        <v>6931958</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 9566-2025 artfynd.xlsx
+++ b/artfynd/A 9566-2025 artfynd.xlsx
@@ -3529,10 +3529,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125869409</v>
+        <v>125871685</v>
       </c>
       <c r="B27" t="n">
-        <v>91242</v>
+        <v>57816</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3540,34 +3540,43 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Palmastjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589372</v>
+        <v>589533</v>
       </c>
       <c r="R27" t="n">
-        <v>6931951</v>
+        <v>6931958</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3599,7 +3608,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3609,7 +3618,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3636,10 +3645,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125871685</v>
+        <v>125869409</v>
       </c>
       <c r="B28" t="n">
-        <v>57816</v>
+        <v>91242</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3647,43 +3656,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Palmastjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589533</v>
+        <v>589372</v>
       </c>
       <c r="R28" t="n">
-        <v>6931958</v>
+        <v>6931951</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3755,7 +3755,7 @@
         <v>125869414</v>
       </c>
       <c r="B29" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 9566-2025 artfynd.xlsx
+++ b/artfynd/A 9566-2025 artfynd.xlsx
@@ -3529,10 +3529,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125869409</v>
+        <v>125871685</v>
       </c>
       <c r="B27" t="n">
-        <v>91242</v>
+        <v>57817</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3540,34 +3540,43 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Palmastjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589372</v>
+        <v>589533</v>
       </c>
       <c r="R27" t="n">
-        <v>6931951</v>
+        <v>6931958</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3599,7 +3608,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3609,7 +3618,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3636,10 +3645,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125871685</v>
+        <v>125869409</v>
       </c>
       <c r="B28" t="n">
-        <v>57816</v>
+        <v>91245</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3647,43 +3656,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Palmastjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589533</v>
+        <v>589372</v>
       </c>
       <c r="R28" t="n">
-        <v>6931958</v>
+        <v>6931951</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3755,7 +3755,7 @@
         <v>125869414</v>
       </c>
       <c r="B29" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>125869329</v>
       </c>
       <c r="B30" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 9566-2025 artfynd.xlsx
+++ b/artfynd/A 9566-2025 artfynd.xlsx
@@ -2042,7 +2042,7 @@
         <v>125296618</v>
       </c>
       <c r="B14" t="n">
-        <v>57648</v>
+        <v>57658</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>125296182</v>
       </c>
       <c r="B18" t="n">
-        <v>57648</v>
+        <v>57658</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 9566-2025 artfynd.xlsx
+++ b/artfynd/A 9566-2025 artfynd.xlsx
@@ -2042,7 +2042,7 @@
         <v>125296618</v>
       </c>
       <c r="B14" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>125296182</v>
       </c>
       <c r="B18" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 9566-2025 artfynd.xlsx
+++ b/artfynd/A 9566-2025 artfynd.xlsx
@@ -2042,7 +2042,7 @@
         <v>125296618</v>
       </c>
       <c r="B14" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>125296182</v>
       </c>
       <c r="B18" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 9566-2025 artfynd.xlsx
+++ b/artfynd/A 9566-2025 artfynd.xlsx
@@ -2042,7 +2042,7 @@
         <v>125296618</v>
       </c>
       <c r="B14" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>125296182</v>
       </c>
       <c r="B18" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 9566-2025 artfynd.xlsx
+++ b/artfynd/A 9566-2025 artfynd.xlsx
@@ -2042,7 +2042,7 @@
         <v>125296618</v>
       </c>
       <c r="B14" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>125296182</v>
       </c>
       <c r="B18" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 9566-2025 artfynd.xlsx
+++ b/artfynd/A 9566-2025 artfynd.xlsx
@@ -2042,7 +2042,7 @@
         <v>125296618</v>
       </c>
       <c r="B14" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>125296182</v>
       </c>
       <c r="B18" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 9566-2025 artfynd.xlsx
+++ b/artfynd/A 9566-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>125296955</v>
       </c>
       <c r="B3" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>125297742</v>
       </c>
       <c r="B5" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>125297544</v>
       </c>
       <c r="B6" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>125297670</v>
       </c>
       <c r="B8" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>125297656</v>
       </c>
       <c r="B13" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>125298021</v>
       </c>
       <c r="B16" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>125296923</v>
       </c>
       <c r="B17" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>125297753</v>
       </c>
       <c r="B20" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>125299459</v>
       </c>
       <c r="B22" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>125298189</v>
       </c>
       <c r="B23" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>125295328</v>
       </c>
       <c r="B24" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>125296301</v>
       </c>
       <c r="B26" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 9566-2025 artfynd.xlsx
+++ b/artfynd/A 9566-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>125296955</v>
       </c>
       <c r="B3" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>125297742</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>125297544</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>125297670</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>125297656</v>
       </c>
       <c r="B13" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>125298021</v>
       </c>
       <c r="B16" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>125296923</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>125297753</v>
       </c>
       <c r="B20" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>125299459</v>
       </c>
       <c r="B22" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>125298189</v>
       </c>
       <c r="B23" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>125295328</v>
       </c>
       <c r="B24" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>125296301</v>
       </c>
       <c r="B26" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 9566-2025 artfynd.xlsx
+++ b/artfynd/A 9566-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125296849</v>
+        <v>125869409</v>
       </c>
       <c r="B2" t="n">
-        <v>78968</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palmastjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589642</v>
+        <v>589372</v>
       </c>
       <c r="R2" t="n">
-        <v>6932043</v>
+        <v>6931951</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,62 +770,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125296955</v>
+        <v>125294611</v>
       </c>
       <c r="B3" t="n">
-        <v>57741</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589631</v>
+        <v>589420</v>
       </c>
       <c r="R3" t="n">
-        <v>6932054</v>
+        <v>6931807</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,62 +877,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125295606</v>
+        <v>125294642</v>
       </c>
       <c r="B4" t="n">
-        <v>56843</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589420</v>
+        <v>589418</v>
       </c>
       <c r="R4" t="n">
-        <v>6932027</v>
+        <v>6931797</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,62 +984,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125297742</v>
+        <v>125296571</v>
       </c>
       <c r="B5" t="n">
-        <v>57741</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589316</v>
+        <v>589603</v>
       </c>
       <c r="R5" t="n">
-        <v>6931994</v>
+        <v>6931964</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,12 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,50 +1103,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125297544</v>
+        <v>125296711</v>
       </c>
       <c r="B6" t="n">
-        <v>57741</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589525</v>
+        <v>589389</v>
       </c>
       <c r="R6" t="n">
-        <v>6931804</v>
+        <v>6931877</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,12 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:43</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,50 +1210,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125299018</v>
+        <v>125296849</v>
       </c>
       <c r="B7" t="n">
-        <v>57811</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589580</v>
+        <v>589642</v>
       </c>
       <c r="R7" t="n">
-        <v>6931659</v>
+        <v>6932043</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,62 +1305,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125297670</v>
+        <v>125297600</v>
       </c>
       <c r="B8" t="n">
-        <v>57741</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589347</v>
+        <v>589363</v>
       </c>
       <c r="R8" t="n">
-        <v>6932010</v>
+        <v>6932050</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,12 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:49</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125301710</v>
+        <v>125294462</v>
       </c>
       <c r="B9" t="n">
-        <v>57651</v>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1485,39 +1435,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589415</v>
+        <v>589418</v>
       </c>
       <c r="R9" t="n">
-        <v>6931910</v>
+        <v>6931797</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1549,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,12 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>20:04</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Trummande tretå.</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,22 +1519,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125296789</v>
+        <v>125296182</v>
       </c>
       <c r="B10" t="n">
-        <v>97212</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1602,34 +1542,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589642</v>
+        <v>589542</v>
       </c>
       <c r="R10" t="n">
-        <v>6932043</v>
+        <v>6932034</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1661,7 +1606,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1671,7 +1616,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,10 +1643,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125299074</v>
+        <v>125296618</v>
       </c>
       <c r="B11" t="n">
-        <v>56843</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1709,39 +1654,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589570</v>
+        <v>589671</v>
       </c>
       <c r="R11" t="n">
-        <v>6931668</v>
+        <v>6931998</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1773,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1783,12 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:35</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Misstänkt natt träd</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1803,22 +1743,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125296711</v>
+        <v>125295328</v>
       </c>
       <c r="B12" t="n">
-        <v>78968</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,34 +1766,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589389</v>
+        <v>589415</v>
       </c>
       <c r="R12" t="n">
-        <v>6931877</v>
+        <v>6932018</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1885,7 +1830,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1895,7 +1840,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1910,22 +1860,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125297656</v>
+        <v>125296301</v>
       </c>
       <c r="B13" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1953,19 +1903,19 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589540</v>
+        <v>589577</v>
       </c>
       <c r="R13" t="n">
-        <v>6931801</v>
+        <v>6932028</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1997,7 +1947,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2007,12 +1957,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2027,22 +1977,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125296618</v>
+        <v>125296740</v>
       </c>
       <c r="B14" t="n">
-        <v>57681</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2050,16 +2000,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2079,10 +2029,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589671</v>
+        <v>589642</v>
       </c>
       <c r="R14" t="n">
-        <v>6931998</v>
+        <v>6932043</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2114,7 +2064,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2124,7 +2074,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2151,10 +2106,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125297600</v>
+        <v>125296955</v>
       </c>
       <c r="B15" t="n">
-        <v>78968</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,34 +2117,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589363</v>
+        <v>589631</v>
       </c>
       <c r="R15" t="n">
-        <v>6932050</v>
+        <v>6932054</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2221,7 +2181,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2231,7 +2191,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2258,10 +2223,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125298021</v>
+        <v>125297544</v>
       </c>
       <c r="B16" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2289,7 +2254,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2298,10 +2263,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589552</v>
+        <v>589525</v>
       </c>
       <c r="R16" t="n">
-        <v>6931786</v>
+        <v>6931804</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2333,7 +2298,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2343,7 +2308,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2375,10 +2340,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125296923</v>
+        <v>125297656</v>
       </c>
       <c r="B17" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2406,19 +2371,19 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589642</v>
+        <v>589540</v>
       </c>
       <c r="R17" t="n">
-        <v>6932043</v>
+        <v>6931801</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2450,7 +2415,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2460,12 +2425,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2480,22 +2445,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125296182</v>
+        <v>125297670</v>
       </c>
       <c r="B18" t="n">
-        <v>57681</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2503,16 +2468,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2532,10 +2497,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589542</v>
+        <v>589347</v>
       </c>
       <c r="R18" t="n">
-        <v>6932034</v>
+        <v>6932010</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2567,7 +2532,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2577,7 +2542,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2604,10 +2574,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125296571</v>
+        <v>125297742</v>
       </c>
       <c r="B19" t="n">
-        <v>78968</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2615,34 +2585,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589603</v>
+        <v>589316</v>
       </c>
       <c r="R19" t="n">
-        <v>6931964</v>
+        <v>6931994</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2674,7 +2649,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2684,7 +2659,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2714,7 +2694,7 @@
         <v>125297753</v>
       </c>
       <c r="B20" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2828,10 +2808,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125299639</v>
+        <v>125298021</v>
       </c>
       <c r="B21" t="n">
-        <v>57811</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2839,36 +2819,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2877,10 +2848,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589495</v>
+        <v>589552</v>
       </c>
       <c r="R21" t="n">
-        <v>6931745</v>
+        <v>6931786</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2912,7 +2883,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2922,7 +2893,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2949,10 +2925,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125299459</v>
+        <v>125298114</v>
       </c>
       <c r="B22" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2989,10 +2965,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589543</v>
+        <v>589559</v>
       </c>
       <c r="R22" t="n">
-        <v>6931727</v>
+        <v>6931779</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3024,7 +3000,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3034,12 +3010,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3066,10 +3042,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125298189</v>
+        <v>125299459</v>
       </c>
       <c r="B23" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3106,10 +3082,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589559</v>
+        <v>589543</v>
       </c>
       <c r="R23" t="n">
-        <v>6931779</v>
+        <v>6931727</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3141,7 +3117,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3151,12 +3127,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3183,10 +3159,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125295328</v>
+        <v>125301710</v>
       </c>
       <c r="B24" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3214,7 +3190,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3226,7 +3202,7 @@
         <v>589415</v>
       </c>
       <c r="R24" t="n">
-        <v>6932018</v>
+        <v>6931910</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3258,7 +3234,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3268,12 +3244,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Trummande tretå.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3300,50 +3276,57 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125295640</v>
+        <v>124844276</v>
       </c>
       <c r="B25" t="n">
-        <v>57811</v>
+        <v>57141</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Pallamstjärn, Västanbäck,  Stöde, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589461</v>
+        <v>589586</v>
       </c>
       <c r="R25" t="n">
-        <v>6932074</v>
+        <v>6931637</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3370,22 +3353,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3400,50 +3383,50 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Thomas Löfqvist</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Thomas Löfqvist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125296301</v>
+        <v>125295606</v>
       </c>
       <c r="B26" t="n">
-        <v>57741</v>
+        <v>57141</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3452,10 +3435,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589577</v>
+        <v>589420</v>
       </c>
       <c r="R26" t="n">
-        <v>6932028</v>
+        <v>6932027</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3487,7 +3470,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3497,12 +3480,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:49</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3529,54 +3507,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125871685</v>
+        <v>125296528</v>
       </c>
       <c r="B27" t="n">
-        <v>57817</v>
+        <v>57141</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Palmastjärnen, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589533</v>
+        <v>589358</v>
       </c>
       <c r="R27" t="n">
-        <v>6931958</v>
+        <v>6931874</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3603,22 +3577,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Fjäder ( dun )</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3645,45 +3624,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125869409</v>
+        <v>125299074</v>
       </c>
       <c r="B28" t="n">
-        <v>91245</v>
+        <v>57141</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Palmastjärnen, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589372</v>
+        <v>589570</v>
       </c>
       <c r="R28" t="n">
-        <v>6931951</v>
+        <v>6931668</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3710,22 +3694,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Misstänkt natt träd</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3752,49 +3741,60 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125869414</v>
+        <v>125869329</v>
       </c>
       <c r="B29" t="n">
-        <v>98361</v>
+        <v>57141</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>36</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palmastjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>589371</v>
+        <v>589374</v>
       </c>
       <c r="R29" t="n">
-        <v>6931943</v>
+        <v>6931940</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3824,9 +3824,24 @@
           <t>2025-06-11</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Fjäder av tjäder tupp</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3841,72 +3856,62 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125869329</v>
+        <v>125295640</v>
       </c>
       <c r="B30" t="n">
-        <v>56849</v>
+        <v>58114</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Palmastjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>589374</v>
+        <v>589461</v>
       </c>
       <c r="R30" t="n">
-        <v>6931940</v>
+        <v>6932074</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3933,27 +3938,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Fjäder av tjäder tupp</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3968,15 +3968,684 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>125299018</v>
+      </c>
+      <c r="B31" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Palamstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>589580</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6931659</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
           <t>Linnea Silverliv</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
+      <c r="AX31" t="inlineStr">
         <is>
           <t>Linnea Silverliv</t>
         </is>
       </c>
-      <c r="AY30" t="inlineStr"/>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>125299639</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Palamstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>589495</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6931745</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>18:58</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>18:58</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>125871685</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Palmastjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>589533</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6931958</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>125867683</v>
+      </c>
+      <c r="B34" t="n">
+        <v>56522</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Palmastjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>589391</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6931834</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>125869414</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Kångeråbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>589371</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6931943</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>125296789</v>
+      </c>
+      <c r="B36" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kångeråbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>589642</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6932043</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9566-2025 artfynd.xlsx
+++ b/artfynd/A 9566-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125869409</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125294611</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125294642</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125296571</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125296711</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125296849</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125297600</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125294462</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1640,6 +1685,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125296182</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1757,6 +1807,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125295328</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1874,6 +1929,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125296301</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1991,6 +2051,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125296740</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2108,6 +2173,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125296955</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2225,6 +2295,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125297544</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2342,6 +2417,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125297656</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2459,6 +2539,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125297670</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2576,6 +2661,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125297742</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2693,6 +2783,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125297753</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2810,6 +2905,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125298021</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2927,6 +3027,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125298114</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3044,6 +3149,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125299459</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3161,6 +3271,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125301710</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3280,6 +3395,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124844276</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3392,6 +3512,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125295606</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3509,6 +3634,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125296528</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3626,6 +3756,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125299074</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3753,6 +3888,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125869329</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3865,6 +4005,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125295640</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3977,6 +4122,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125299018</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4098,6 +4248,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125299639</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4214,6 +4369,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125871685</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4326,6 +4486,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125867683</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4427,6 +4592,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125869414</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4534,6 +4704,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125296789</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4646,8 +4821,50 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125296618</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>